--- a/output/graficos_dimensiones/comunal_e_rezmat_a_2021_metropolitana.xlsx
+++ b/output/graficos_dimensiones/comunal_e_rezmat_a_2021_metropolitana.xlsx
@@ -201,7 +201,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-06 21:46</t>
+    <t xml:space="preserve">2026-09-10 00:56</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_e_rezmat_a_2021_metropolitana.xlsx
+++ b/output/graficos_dimensiones/comunal_e_rezmat_a_2021_metropolitana.xlsx
@@ -201,7 +201,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-10 00:56</t>
+    <t xml:space="preserve">2026-09-18 11:04</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_e_rezmat_a_2021_metropolitana.xlsx
+++ b/output/graficos_dimensiones/comunal_e_rezmat_a_2021_metropolitana.xlsx
@@ -201,7 +201,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-18 11:04</t>
+    <t xml:space="preserve">2026-09-23 14:26</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -1483,7 +1483,9 @@
       <c r="C52" s="2" t="n">
         <v>13106</v>
       </c>
-      <c r="D52" s="2"/>
+      <c r="D52" s="2" t="n">
+        <v>2021</v>
+      </c>
       <c r="E52" s="2"/>
     </row>
     <row r="53">
@@ -1496,7 +1498,9 @@
       <c r="C53" s="2" t="n">
         <v>13303</v>
       </c>
-      <c r="D53" s="2"/>
+      <c r="D53" s="2" t="n">
+        <v>2021</v>
+      </c>
       <c r="E53" s="2"/>
     </row>
   </sheetData>

--- a/output/graficos_dimensiones/comunal_e_rezmat_a_2021_metropolitana.xlsx
+++ b/output/graficos_dimensiones/comunal_e_rezmat_a_2021_metropolitana.xlsx
@@ -201,7 +201,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-23 14:26</t>
+    <t xml:space="preserve">2026-10-02 16:10</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_e_rezmat_a_2021_metropolitana.xlsx
+++ b/output/graficos_dimensiones/comunal_e_rezmat_a_2021_metropolitana.xlsx
@@ -201,7 +201,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-02 16:10</t>
+    <t xml:space="preserve">2026-10-05 14:51</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
